--- a/src/main/resources/PermanentRecordSetup_Field_Values.xlsx
+++ b/src/main/resources/PermanentRecordSetup_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a1f75072f6ba4249/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="160" documentId="8_{63F9D79F-3AE2-47C5-80C3-1AA1130FD41A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{8E6EF3FC-62CE-416D-99EA-C2DCEAFED33F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CCA97E-04FC-40F9-AD8D-E54E9B3338FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="29" activeTab="34" xr2:uid="{A0F3250E-2737-4AB5-82B5-97D4AA917802}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="31" activeTab="35" xr2:uid="{A0F3250E-2737-4AB5-82B5-97D4AA917802}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationFundingSource" sheetId="1" r:id="rId1"/>
@@ -48,6 +48,7 @@
     <sheet name="Grant_Creation2" sheetId="34" r:id="rId33"/>
     <sheet name="Grant_Edition2" sheetId="33" r:id="rId34"/>
     <sheet name="StrategicGoalCreation" sheetId="35" r:id="rId35"/>
+    <sheet name="StrategicPlanCreation" sheetId="36" r:id="rId36"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="171">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -574,6 +575,12 @@
   </si>
   <si>
     <t>Automation Permanent Strategic Goal</t>
+  </si>
+  <si>
+    <t>StrategyTitle__c</t>
+  </si>
+  <si>
+    <t>Automation Permanent Strategic Plan</t>
   </si>
 </sst>
 </file>
@@ -4132,6 +4139,64 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03367B2B-715C-4659-A6C4-721231659FD4}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>730</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{506C7784-46A1-4098-9646-BE6C85090D64}">
   <dimension ref="A1:C7"/>

--- a/src/main/resources/PermanentRecordSetup_Field_Values.xlsx
+++ b/src/main/resources/PermanentRecordSetup_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CCA97E-04FC-40F9-AD8D-E54E9B3338FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3403A4A-05A3-4398-A29F-8940E8F471A2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="31" activeTab="35" xr2:uid="{A0F3250E-2737-4AB5-82B5-97D4AA917802}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="18" activeTab="22" xr2:uid="{A0F3250E-2737-4AB5-82B5-97D4AA917802}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationFundingSource" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="172">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -581,6 +581,9 @@
   </si>
   <si>
     <t>Automation Permanent Strategic Plan</t>
+  </si>
+  <si>
+    <t>MaxApplicationsAllowed__c</t>
   </si>
 </sst>
 </file>
@@ -2639,7 +2642,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB919764-9A5C-4A4C-85EB-9571B28F299A}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -2704,13 +2707,13 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="C6">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2718,10 +2721,10 @@
         <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C7">
-        <v>10000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2729,10 +2732,10 @@
         <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2740,9 +2743,20 @@
         <v>70</v>
       </c>
       <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" t="s">
         <v>74</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>10000</v>
       </c>
     </row>
